--- a/output/yearly_benthic_cover_iteration_41_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_41_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.23289426536662</v>
+        <v>45.32337208957788</v>
       </c>
       <c r="M2" t="n">
-        <v>99.94828146687971</v>
+        <v>100.7493704301564</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.03650256709342</v>
+        <v>87.99207848347623</v>
       </c>
       <c r="C3" t="n">
-        <v>45.95354869743651</v>
+        <v>45.90008524000941</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228735339986698</v>
+        <v>2.228661905798022</v>
       </c>
       <c r="E3" t="n">
-        <v>5.720967790487847</v>
+        <v>5.688132814421119</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429117799955661</v>
+        <v>0.742887301932674</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98167591443674</v>
+        <v>33.96355608088611</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17394187979603</v>
+        <v>34.172815888903</v>
       </c>
       <c r="I3" t="n">
-        <v>6.545071237418239</v>
+        <v>6.552978854456092</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643198624972288</v>
+        <v>4.643045637079213</v>
       </c>
       <c r="K3" t="n">
-        <v>11.96349743290658</v>
+        <v>12.00792151652375</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84801987386152</v>
+        <v>48.85676765496791</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7650660042046</v>
+        <v>106.7647744115011</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.1455635896039</v>
+        <v>87.07546615276421</v>
       </c>
       <c r="C4" t="n">
-        <v>42.69238951928097</v>
+        <v>42.61676172433368</v>
       </c>
       <c r="D4" t="n">
-        <v>2.185940600625848</v>
+        <v>2.184450894126464</v>
       </c>
       <c r="E4" t="n">
-        <v>6.522055572278472</v>
+        <v>6.487337189806182</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444649208108234</v>
+        <v>0.7444435263147517</v>
       </c>
       <c r="G4" t="n">
-        <v>33.32918167803633</v>
+        <v>33.28980508689583</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24538635729787</v>
+        <v>34.24440221047858</v>
       </c>
       <c r="I4" t="n">
-        <v>5.465628705486907</v>
+        <v>5.4722552056752</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652905755067646</v>
+        <v>4.652772039467199</v>
       </c>
       <c r="K4" t="n">
-        <v>12.85443641039611</v>
+        <v>12.92453384723579</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27136653595019</v>
+        <v>44.27667723802896</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81819246562726</v>
+        <v>99.81797280959843</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.99609802704374</v>
+        <v>85.84304610599378</v>
       </c>
       <c r="C5" t="n">
-        <v>42.39129230717562</v>
+        <v>42.23365209560546</v>
       </c>
       <c r="D5" t="n">
-        <v>2.12992850253167</v>
+        <v>2.124054333976765</v>
       </c>
       <c r="E5" t="n">
-        <v>7.115393403243804</v>
+        <v>7.069356401676125</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745781571365</v>
+        <v>0.7457640925570663</v>
       </c>
       <c r="G5" t="n">
-        <v>32.47516149422422</v>
+        <v>32.36939542206495</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30595228278999</v>
+        <v>34.30514825762504</v>
       </c>
       <c r="I5" t="n">
-        <v>4.562745951857811</v>
+        <v>4.568302019612153</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66113482103125</v>
+        <v>4.661025578481665</v>
       </c>
       <c r="K5" t="n">
-        <v>14.00390197295626</v>
+        <v>14.15695389400622</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45298270027126</v>
+        <v>43.45738692134178</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84817698040314</v>
+        <v>99.84799291095347</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.62200240195185</v>
+        <v>84.37630626913483</v>
       </c>
       <c r="C6" t="n">
-        <v>41.72588406180861</v>
+        <v>41.47631680502874</v>
       </c>
       <c r="D6" t="n">
-        <v>2.062867366794547</v>
+        <v>2.052183418841681</v>
       </c>
       <c r="E6" t="n">
-        <v>7.526029404701071</v>
+        <v>7.465595017879631</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469002441979524</v>
+        <v>0.7468873696785298</v>
       </c>
       <c r="G6" t="n">
-        <v>31.45267589883425</v>
+        <v>31.27412302995173</v>
       </c>
       <c r="H6" t="n">
-        <v>34.3574112331058</v>
+        <v>34.35681900521236</v>
       </c>
       <c r="I6" t="n">
-        <v>3.807991728081016</v>
+        <v>3.812652367080085</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668126526237202</v>
+        <v>4.668046060490812</v>
       </c>
       <c r="K6" t="n">
-        <v>15.37799759804816</v>
+        <v>15.62369373086518</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76937539703608</v>
+        <v>42.7730921857835</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87325705689284</v>
+        <v>99.87310272167743</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.03468396677306</v>
+        <v>82.70374385034755</v>
       </c>
       <c r="C7" t="n">
-        <v>40.73004221936029</v>
+        <v>40.39576146854765</v>
       </c>
       <c r="D7" t="n">
-        <v>1.985613646606536</v>
+        <v>1.970562567900537</v>
       </c>
       <c r="E7" t="n">
-        <v>7.773744368583645</v>
+        <v>7.698882257352707</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478529310214659</v>
+        <v>0.7478450292408423</v>
       </c>
       <c r="G7" t="n">
-        <v>30.27478329063017</v>
+        <v>30.03026709061104</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40123482698742</v>
+        <v>34.40087134507873</v>
       </c>
       <c r="I7" t="n">
-        <v>3.177374084059658</v>
+        <v>3.181284127408436</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674080818884161</v>
+        <v>4.674031432755266</v>
       </c>
       <c r="K7" t="n">
-        <v>16.96531603322695</v>
+        <v>17.29625614965244</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19886419941052</v>
+        <v>42.20207537160324</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89422245199773</v>
+        <v>99.89409298980333</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.06896819824085</v>
+        <v>87.47945610573659</v>
       </c>
       <c r="C8" t="n">
-        <v>43.11461097556779</v>
+        <v>42.68400017831041</v>
       </c>
       <c r="D8" t="n">
-        <v>1.989898666974059</v>
+        <v>1.974728168028948</v>
       </c>
       <c r="E8" t="n">
-        <v>9.665713713241116</v>
+        <v>9.517477724359656</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494668225490626</v>
+        <v>0.7494259094425585</v>
       </c>
       <c r="G8" t="n">
-        <v>30.80257453894484</v>
+        <v>30.53259868914234</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47547383725687</v>
+        <v>34.47359183435768</v>
       </c>
       <c r="I8" t="n">
-        <v>5.701672978343251</v>
+        <v>5.54772184638941</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684167640931642</v>
+        <v>4.683911934015992</v>
       </c>
       <c r="K8" t="n">
-        <v>11.93103180175917</v>
+        <v>12.52054389426345</v>
       </c>
       <c r="L8" t="n">
-        <v>44.76471072019558</v>
+        <v>44.61092195485865</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81035349752254</v>
+        <v>99.81546602743249</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.04777690397987</v>
+        <v>85.26261941881795</v>
       </c>
       <c r="C9" t="n">
-        <v>41.978361472218</v>
+        <v>41.32791072716451</v>
       </c>
       <c r="D9" t="n">
-        <v>1.898665669395238</v>
+        <v>1.873946895536277</v>
       </c>
       <c r="E9" t="n">
-        <v>10.01591875537953</v>
+        <v>9.803660405072138</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508488372468483</v>
+        <v>0.7507828719951901</v>
       </c>
       <c r="G9" t="n">
-        <v>29.39033618984016</v>
+        <v>28.9743517373752</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53904651335501</v>
+        <v>34.53601211177873</v>
       </c>
       <c r="I9" t="n">
-        <v>4.760155705970281</v>
+        <v>4.631472447090457</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692805232792802</v>
+        <v>4.69239294996994</v>
       </c>
       <c r="K9" t="n">
-        <v>13.95222309602014</v>
+        <v>14.73738058118207</v>
       </c>
       <c r="L9" t="n">
-        <v>43.91103562680789</v>
+        <v>43.78060530703151</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84162019504602</v>
+        <v>99.84589661537808</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.83090361800811</v>
+        <v>82.79767838413203</v>
       </c>
       <c r="C10" t="n">
-        <v>40.50002890283036</v>
+        <v>39.58106093738881</v>
       </c>
       <c r="D10" t="n">
-        <v>1.799601039208109</v>
+        <v>1.763059149843033</v>
       </c>
       <c r="E10" t="n">
-        <v>10.15550615804026</v>
+        <v>9.867805941497883</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520350226542437</v>
+        <v>0.7519512627651227</v>
       </c>
       <c r="G10" t="n">
-        <v>27.85686832730211</v>
+        <v>27.2598418146374</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5936110420952</v>
+        <v>34.58975808719563</v>
       </c>
       <c r="I10" t="n">
-        <v>3.973063137119165</v>
+        <v>3.865566735910936</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700218891589024</v>
+        <v>4.699695392282019</v>
       </c>
       <c r="K10" t="n">
-        <v>16.16909638199188</v>
+        <v>17.20232161586798</v>
       </c>
       <c r="L10" t="n">
-        <v>43.19864816778971</v>
+        <v>43.08796543432405</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86777345261196</v>
+        <v>99.87134798758083</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.4230492603196</v>
+        <v>80.12946744897229</v>
       </c>
       <c r="C11" t="n">
-        <v>38.70797051411608</v>
+        <v>37.51133150246022</v>
       </c>
       <c r="D11" t="n">
-        <v>1.693054798958422</v>
+        <v>1.644302744155377</v>
       </c>
       <c r="E11" t="n">
-        <v>10.10680784160068</v>
+        <v>9.740733453594778</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530557334842451</v>
+        <v>0.7529602611577857</v>
       </c>
       <c r="G11" t="n">
-        <v>26.20758911444354</v>
+        <v>25.42366925411461</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64056374027527</v>
+        <v>34.63617201325813</v>
       </c>
       <c r="I11" t="n">
-        <v>3.315379697280917</v>
+        <v>3.225628090455444</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706598334276532</v>
+        <v>4.706001632236163</v>
       </c>
       <c r="K11" t="n">
-        <v>18.57695073968041</v>
+        <v>19.8705325510277</v>
       </c>
       <c r="L11" t="n">
-        <v>42.60471588128353</v>
+        <v>42.51075909273676</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88963713508002</v>
+        <v>99.89262314622469</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.89238622438998</v>
+        <v>77.41512452062582</v>
       </c>
       <c r="C12" t="n">
-        <v>36.6903138549574</v>
+        <v>35.29532668612821</v>
       </c>
       <c r="D12" t="n">
-        <v>1.582172483780298</v>
+        <v>1.524813607400674</v>
       </c>
       <c r="E12" t="n">
-        <v>9.905895737037412</v>
+        <v>9.481411262202743</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539358295175392</v>
+        <v>0.7538327522016742</v>
       </c>
       <c r="G12" t="n">
-        <v>24.49118976456172</v>
+        <v>23.5761674463671</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6810481578068</v>
+        <v>34.67630660127701</v>
       </c>
       <c r="I12" t="n">
-        <v>2.766045317201601</v>
+        <v>2.691138149916156</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71209893448462</v>
+        <v>4.711454701260466</v>
       </c>
       <c r="K12" t="n">
-        <v>21.10761377561001</v>
+        <v>22.58487547937419</v>
       </c>
       <c r="L12" t="n">
-        <v>42.10997848895257</v>
+        <v>42.03019705420716</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90790611951998</v>
+        <v>99.91039921970956</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.35662026372893</v>
+        <v>74.80424292515733</v>
       </c>
       <c r="C13" t="n">
-        <v>34.58160081495834</v>
+        <v>33.09911266019206</v>
       </c>
       <c r="D13" t="n">
-        <v>1.47214461990093</v>
+        <v>1.411104258735382</v>
       </c>
       <c r="E13" t="n">
-        <v>9.601577202605315</v>
+        <v>9.148500643198419</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546952489555212</v>
+        <v>0.7545868305681461</v>
       </c>
       <c r="G13" t="n">
-        <v>22.78801686698961</v>
+        <v>21.81803082472439</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71598145195397</v>
+        <v>34.71099420613471</v>
       </c>
       <c r="I13" t="n">
-        <v>2.307359567351561</v>
+        <v>2.244858470745357</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716845305972008</v>
+        <v>4.716167691050915</v>
       </c>
       <c r="K13" t="n">
-        <v>23.64337973627108</v>
+        <v>25.19575707484268</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69818485662609</v>
+        <v>41.6303764274676</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92316540785552</v>
+        <v>99.92524616250233</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.22462172313165</v>
+        <v>82.29743955628688</v>
       </c>
       <c r="C14" t="n">
-        <v>38.8529541932141</v>
+        <v>37.84894468787268</v>
       </c>
       <c r="D14" t="n">
-        <v>1.473897325856646</v>
+        <v>1.412708197805398</v>
       </c>
       <c r="E14" t="n">
-        <v>11.98150466135586</v>
+        <v>11.75380058605453</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555937740322786</v>
+        <v>0.7554445356539152</v>
       </c>
       <c r="G14" t="n">
-        <v>24.68821598254622</v>
+        <v>23.97001257020693</v>
       </c>
       <c r="H14" t="n">
-        <v>36.63038176370083</v>
+        <v>36.87763080618786</v>
       </c>
       <c r="I14" t="n">
-        <v>2.972567127938082</v>
+        <v>2.806314512541284</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722461087701742</v>
+        <v>4.721528347836971</v>
       </c>
       <c r="K14" t="n">
-        <v>16.77537827686835</v>
+        <v>17.70256044371312</v>
       </c>
       <c r="L14" t="n">
-        <v>44.2726997880014</v>
+        <v>44.35505725768068</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90103225808384</v>
+        <v>99.90656238926648</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.32640111356214</v>
+        <v>81.39183620398144</v>
       </c>
       <c r="C15" t="n">
-        <v>38.40123549426124</v>
+        <v>37.37612844193497</v>
       </c>
       <c r="D15" t="n">
-        <v>1.439170843757479</v>
+        <v>1.379579489392634</v>
       </c>
       <c r="E15" t="n">
-        <v>12.12510442796556</v>
+        <v>11.86830768991053</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563523764371651</v>
+        <v>0.7561687576730997</v>
       </c>
       <c r="G15" t="n">
-        <v>24.11916198801926</v>
+        <v>23.40790387831834</v>
       </c>
       <c r="H15" t="n">
-        <v>36.67978284859743</v>
+        <v>36.91298428481495</v>
       </c>
       <c r="I15" t="n">
-        <v>2.479626276052976</v>
+        <v>2.340837368415011</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727202352732284</v>
+        <v>4.726054735456874</v>
       </c>
       <c r="K15" t="n">
-        <v>17.67359888643784</v>
+        <v>18.60816379601855</v>
       </c>
       <c r="L15" t="n">
-        <v>43.84259431019153</v>
+        <v>43.93775458114257</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91742869089062</v>
+        <v>99.9220468190961</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.72973734069159</v>
+        <v>78.79777406252714</v>
       </c>
       <c r="C16" t="n">
-        <v>36.1875184016496</v>
+        <v>35.14301397500905</v>
       </c>
       <c r="D16" t="n">
-        <v>1.341160100154299</v>
+        <v>1.283007942755337</v>
       </c>
       <c r="E16" t="n">
-        <v>11.64404809543919</v>
+        <v>11.36290250632931</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570063541085513</v>
+        <v>0.7567932571019875</v>
       </c>
       <c r="G16" t="n">
-        <v>22.47659327438453</v>
+        <v>21.76933393838571</v>
       </c>
       <c r="H16" t="n">
-        <v>36.71149790591934</v>
+        <v>36.94346972522822</v>
       </c>
       <c r="I16" t="n">
-        <v>2.068141897507223</v>
+        <v>1.952308835839144</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731289713178447</v>
+        <v>4.729957856887423</v>
       </c>
       <c r="K16" t="n">
-        <v>20.2702626593084</v>
+        <v>21.20222593747286</v>
       </c>
       <c r="L16" t="n">
-        <v>43.47334043137386</v>
+        <v>43.58973682728434</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93112149233185</v>
+        <v>99.93497673976626</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.57841735517357</v>
+        <v>80.78152292615937</v>
       </c>
       <c r="C17" t="n">
-        <v>37.52097562220774</v>
+        <v>36.57834015966233</v>
       </c>
       <c r="D17" t="n">
-        <v>1.342293736767223</v>
+        <v>1.284026678483953</v>
       </c>
       <c r="E17" t="n">
-        <v>12.47791324008485</v>
+        <v>12.23599010787438</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576462256042324</v>
+        <v>0.7573941671232691</v>
       </c>
       <c r="G17" t="n">
-        <v>22.9748376129734</v>
+        <v>22.32997319006605</v>
       </c>
       <c r="H17" t="n">
-        <v>37.22177452094554</v>
+        <v>37.51615756504414</v>
       </c>
       <c r="I17" t="n">
-        <v>2.068663108771867</v>
+        <v>1.924267673047147</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735288910026454</v>
+        <v>4.733713544520433</v>
       </c>
       <c r="K17" t="n">
-        <v>18.42158264482645</v>
+        <v>19.21847707384063</v>
       </c>
       <c r="L17" t="n">
-        <v>43.98854453244624</v>
+        <v>44.13909140064312</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93110279948043</v>
+        <v>99.93590863414609</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.06831427738643</v>
+        <v>78.22277424962685</v>
       </c>
       <c r="C18" t="n">
-        <v>35.32990205830534</v>
+        <v>34.31589486604943</v>
       </c>
       <c r="D18" t="n">
-        <v>1.251634084048073</v>
+        <v>1.193196208478388</v>
       </c>
       <c r="E18" t="n">
-        <v>11.92266771874787</v>
+        <v>11.63787334766178</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581972451331161</v>
+        <v>0.7579120703205871</v>
       </c>
       <c r="G18" t="n">
-        <v>21.42309767541885</v>
+        <v>20.75037831555759</v>
       </c>
       <c r="H18" t="n">
-        <v>37.24884510345176</v>
+        <v>37.54181096824873</v>
       </c>
       <c r="I18" t="n">
-        <v>1.725139668504777</v>
+        <v>1.604652899856102</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738732782081977</v>
+        <v>4.73695043950367</v>
       </c>
       <c r="K18" t="n">
-        <v>20.93168572261357</v>
+        <v>21.77722575037317</v>
       </c>
       <c r="L18" t="n">
-        <v>43.68094935494855</v>
+        <v>43.85342750377053</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94253713586745</v>
+        <v>99.94654812019313</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.07575753091587</v>
+        <v>77.23761006336923</v>
       </c>
       <c r="C19" t="n">
-        <v>34.60243981408858</v>
+        <v>33.56741827017218</v>
       </c>
       <c r="D19" t="n">
-        <v>1.21646445208649</v>
+        <v>1.158467138119034</v>
       </c>
       <c r="E19" t="n">
-        <v>11.82743565209599</v>
+        <v>11.52369711709511</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586629531812638</v>
+        <v>0.7583527694973885</v>
       </c>
       <c r="G19" t="n">
-        <v>20.82113063862746</v>
+        <v>20.14641951700995</v>
       </c>
       <c r="H19" t="n">
-        <v>37.2717244888099</v>
+        <v>37.56364020918211</v>
       </c>
       <c r="I19" t="n">
-        <v>1.438695888731856</v>
+        <v>1.347328503106956</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741643457382898</v>
+        <v>4.739704809358679</v>
       </c>
       <c r="K19" t="n">
-        <v>21.92424246908413</v>
+        <v>22.76238993663076</v>
       </c>
       <c r="L19" t="n">
-        <v>43.42539062549523</v>
+        <v>43.6253069420537</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95207290866794</v>
+        <v>99.95511514885663</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.37815045909464</v>
+        <v>74.61200436817748</v>
       </c>
       <c r="C20" t="n">
-        <v>32.12590549760498</v>
+        <v>31.14845980529459</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1201576954265</v>
+        <v>1.066348685045668</v>
       </c>
       <c r="E20" t="n">
-        <v>11.09098957720229</v>
+        <v>10.79458398042581</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590653923247928</v>
+        <v>0.7587333543209074</v>
       </c>
       <c r="G20" t="n">
-        <v>19.172734289387</v>
+        <v>18.54442586539259</v>
       </c>
       <c r="H20" t="n">
-        <v>37.29149558850342</v>
+        <v>37.5824917937675</v>
       </c>
       <c r="I20" t="n">
-        <v>1.199549214220683</v>
+        <v>1.123337224719342</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744158702029955</v>
+        <v>4.742083464505672</v>
       </c>
       <c r="K20" t="n">
-        <v>24.62184954090535</v>
+        <v>25.38799563182252</v>
       </c>
       <c r="L20" t="n">
-        <v>43.21228118680268</v>
+        <v>43.42611877112992</v>
       </c>
       <c r="M20" t="n">
-        <v>99.960036225313</v>
+        <v>99.96257420824702</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.65270620395393</v>
+        <v>81.05387937427153</v>
       </c>
       <c r="C21" t="n">
-        <v>36.05814981705826</v>
+        <v>35.24286851960184</v>
       </c>
       <c r="D21" t="n">
-        <v>1.120929017131669</v>
+        <v>1.067017083486278</v>
       </c>
       <c r="E21" t="n">
-        <v>13.19813774077829</v>
+        <v>12.96903030027275</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595880719574313</v>
+        <v>0.7592089362745206</v>
       </c>
       <c r="G21" t="n">
-        <v>21.0043240212775</v>
+        <v>20.46970279591026</v>
       </c>
       <c r="H21" t="n">
-        <v>39.13556159397383</v>
+        <v>39.51970198191206</v>
       </c>
       <c r="I21" t="n">
-        <v>1.68674030910127</v>
+        <v>1.524162424699905</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747425449733946</v>
+        <v>4.745055851715755</v>
       </c>
       <c r="K21" t="n">
-        <v>18.34729379604609</v>
+        <v>18.94612062572848</v>
       </c>
       <c r="L21" t="n">
-        <v>45.5383703986499</v>
+        <v>45.76023726592624</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94381401175424</v>
+        <v>99.94922641125656</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_41_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_41_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.32337208957788</v>
+        <v>45.35696290104448</v>
       </c>
       <c r="M2" t="n">
-        <v>100.7493704301564</v>
+        <v>99.54986714336655</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.99207848347623</v>
+        <v>87.95498805520982</v>
       </c>
       <c r="C3" t="n">
-        <v>45.90008524000941</v>
+        <v>45.87319237513621</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228661905798022</v>
+        <v>2.228587073419041</v>
       </c>
       <c r="E3" t="n">
-        <v>5.688132814421119</v>
+        <v>5.67078464309845</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742887301932674</v>
+        <v>0.742862357806347</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96355608088611</v>
+        <v>33.95460073554845</v>
       </c>
       <c r="H3" t="n">
-        <v>34.172815888903</v>
+        <v>34.17166845909196</v>
       </c>
       <c r="I3" t="n">
-        <v>6.552978854456092</v>
+        <v>6.543595049955898</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643045637079213</v>
+        <v>4.642889736289669</v>
       </c>
       <c r="K3" t="n">
-        <v>12.00792151652375</v>
+        <v>12.0450119447902</v>
       </c>
       <c r="L3" t="n">
-        <v>48.85676765496791</v>
+        <v>48.8468990452325</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7647744115011</v>
+        <v>106.7651033651589</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.07546615276421</v>
+        <v>86.95732373419496</v>
       </c>
       <c r="C4" t="n">
-        <v>42.61676172433368</v>
+        <v>42.50800313468465</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184450894126464</v>
+        <v>2.180021603018752</v>
       </c>
       <c r="E4" t="n">
-        <v>6.487337189806182</v>
+        <v>6.457943001628195</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444435263147517</v>
+        <v>0.7444184124924271</v>
       </c>
       <c r="G4" t="n">
-        <v>33.28980508689583</v>
+        <v>33.21466053906961</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24440221047858</v>
+        <v>34.24324697465165</v>
       </c>
       <c r="I4" t="n">
-        <v>5.4722552056752</v>
+        <v>5.464418125256652</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652772039467199</v>
+        <v>4.65261507807767</v>
       </c>
       <c r="K4" t="n">
-        <v>12.92453384723579</v>
+        <v>13.04267626580504</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27667723802896</v>
+        <v>44.26755407034488</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81797280959843</v>
+        <v>99.81823347083457</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.84304610599378</v>
+        <v>85.7456224826677</v>
       </c>
       <c r="C5" t="n">
-        <v>42.23365209560546</v>
+        <v>42.14428926652293</v>
       </c>
       <c r="D5" t="n">
-        <v>2.124054333976765</v>
+        <v>2.120660503299093</v>
       </c>
       <c r="E5" t="n">
-        <v>7.069356401676125</v>
+        <v>7.042388700157625</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457640925570663</v>
+        <v>0.7457385405252581</v>
       </c>
       <c r="G5" t="n">
-        <v>32.36939542206495</v>
+        <v>32.3102388701815</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30514825762504</v>
+        <v>34.30397286416187</v>
       </c>
       <c r="I5" t="n">
-        <v>4.568302019612153</v>
+        <v>4.561757126059486</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661025578481665</v>
+        <v>4.660865878282864</v>
       </c>
       <c r="K5" t="n">
-        <v>14.15695389400622</v>
+        <v>14.2543775173323</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45738692134178</v>
+        <v>43.44954382377652</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84799291095347</v>
+        <v>99.84821060763176</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.37630626913483</v>
+        <v>84.30246090862134</v>
       </c>
       <c r="C6" t="n">
-        <v>41.47631680502874</v>
+        <v>41.40944241873646</v>
       </c>
       <c r="D6" t="n">
-        <v>2.052183418841681</v>
+        <v>2.049948371937061</v>
       </c>
       <c r="E6" t="n">
-        <v>7.465595017879631</v>
+        <v>7.442095688952925</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468873696785298</v>
+        <v>0.7468611514797835</v>
       </c>
       <c r="G6" t="n">
-        <v>31.27412302995173</v>
+        <v>31.23287365695073</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35681900521236</v>
+        <v>34.35561296807003</v>
       </c>
       <c r="I6" t="n">
-        <v>3.812652367080085</v>
+        <v>3.807186874482162</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668046060490812</v>
+        <v>4.667882196748647</v>
       </c>
       <c r="K6" t="n">
-        <v>15.62369373086518</v>
+        <v>15.69753909137868</v>
       </c>
       <c r="L6" t="n">
-        <v>42.7730921857835</v>
+        <v>42.76630301416097</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87310272167743</v>
+        <v>99.8732845242761</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.70374385034755</v>
+        <v>82.67196048747341</v>
       </c>
       <c r="C7" t="n">
-        <v>40.39576146854765</v>
+        <v>40.3700544029618</v>
       </c>
       <c r="D7" t="n">
-        <v>1.970562567900537</v>
+        <v>1.970395304221247</v>
       </c>
       <c r="E7" t="n">
-        <v>7.698882257352707</v>
+        <v>7.682740902333238</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478450292408423</v>
+        <v>0.7478177709999619</v>
       </c>
       <c r="G7" t="n">
-        <v>30.03026709061104</v>
+        <v>30.02080854008974</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40087134507873</v>
+        <v>34.39961746599824</v>
       </c>
       <c r="I7" t="n">
-        <v>3.181284127408436</v>
+        <v>3.176719435081222</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674031432755266</v>
+        <v>4.673861068749763</v>
       </c>
       <c r="K7" t="n">
-        <v>17.29625614965244</v>
+        <v>17.32803951252657</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20207537160324</v>
+        <v>42.19615089355382</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89409298980333</v>
+        <v>99.89424480904219</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.47945610573659</v>
+        <v>87.57142461651272</v>
       </c>
       <c r="C8" t="n">
-        <v>42.68400017831041</v>
+        <v>42.63588308356096</v>
       </c>
       <c r="D8" t="n">
-        <v>1.974728168028948</v>
+        <v>1.974659317529403</v>
       </c>
       <c r="E8" t="n">
-        <v>9.517477724359656</v>
+        <v>9.494488036955628</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494259094425585</v>
+        <v>0.7494360782100877</v>
       </c>
       <c r="G8" t="n">
-        <v>30.53259868914234</v>
+        <v>30.50956538682441</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47359183435768</v>
+        <v>34.47405959766403</v>
       </c>
       <c r="I8" t="n">
-        <v>5.54772184638941</v>
+        <v>5.685240710516106</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683911934015992</v>
+        <v>4.683975488813049</v>
       </c>
       <c r="K8" t="n">
-        <v>12.52054389426345</v>
+        <v>12.42857538348728</v>
       </c>
       <c r="L8" t="n">
-        <v>44.61092195485865</v>
+        <v>44.74644272655807</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81546602743249</v>
+        <v>99.81090119360631</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.26261941881795</v>
+        <v>85.51552608909526</v>
       </c>
       <c r="C9" t="n">
-        <v>41.32791072716451</v>
+        <v>41.46186705745152</v>
       </c>
       <c r="D9" t="n">
-        <v>1.873946895536277</v>
+        <v>1.88142526579664</v>
       </c>
       <c r="E9" t="n">
-        <v>9.803660405072138</v>
+        <v>9.83728098765541</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507828719951901</v>
+        <v>0.7508226384529815</v>
       </c>
       <c r="G9" t="n">
-        <v>28.9743517373752</v>
+        <v>29.06904834554651</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53601211177873</v>
+        <v>34.53784136883714</v>
       </c>
       <c r="I9" t="n">
-        <v>4.631472447090457</v>
+        <v>4.74646599247543</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69239294996994</v>
+        <v>4.692641490331135</v>
       </c>
       <c r="K9" t="n">
-        <v>14.73738058118207</v>
+        <v>14.48447391090476</v>
       </c>
       <c r="L9" t="n">
-        <v>43.78060530703151</v>
+        <v>43.89573567857384</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84589661537808</v>
+        <v>99.84207664693011</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.79767838413203</v>
+        <v>83.15332705536431</v>
       </c>
       <c r="C10" t="n">
-        <v>39.58106093738881</v>
+        <v>39.83560959156441</v>
       </c>
       <c r="D10" t="n">
-        <v>1.763059149843033</v>
+        <v>1.775278464717587</v>
       </c>
       <c r="E10" t="n">
-        <v>9.867805941497883</v>
+        <v>9.942556703010819</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519512627651227</v>
+        <v>0.7520150186546708</v>
       </c>
       <c r="G10" t="n">
-        <v>27.2598418146374</v>
+        <v>27.42902227149165</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58975808719563</v>
+        <v>34.59269085811486</v>
       </c>
       <c r="I10" t="n">
-        <v>3.865566735910936</v>
+        <v>3.96166987278303</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699695392282019</v>
+        <v>4.700093866591693</v>
       </c>
       <c r="K10" t="n">
-        <v>17.20232161586798</v>
+        <v>16.8466729446357</v>
       </c>
       <c r="L10" t="n">
-        <v>43.08796543432405</v>
+        <v>43.18587118623113</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87134798758083</v>
+        <v>99.86815372243125</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.12946744897229</v>
+        <v>80.66341344914107</v>
       </c>
       <c r="C11" t="n">
-        <v>37.51133150246022</v>
+        <v>37.95919077842694</v>
       </c>
       <c r="D11" t="n">
-        <v>1.644302744155377</v>
+        <v>1.664633891597228</v>
       </c>
       <c r="E11" t="n">
-        <v>9.740733453594778</v>
+        <v>9.873868551798044</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529602611577857</v>
+        <v>0.7530423690628808</v>
       </c>
       <c r="G11" t="n">
-        <v>25.42366925411461</v>
+        <v>25.71950316186802</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63617201325813</v>
+        <v>34.63994897689252</v>
       </c>
       <c r="I11" t="n">
-        <v>3.225628090455444</v>
+        <v>3.305901691279391</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706001632236163</v>
+        <v>4.706514806643006</v>
       </c>
       <c r="K11" t="n">
-        <v>19.8705325510277</v>
+        <v>19.3365865508589</v>
       </c>
       <c r="L11" t="n">
-        <v>42.51075909273676</v>
+        <v>42.59417628535908</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89262314622469</v>
+        <v>99.88995361464492</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.41512452062582</v>
+        <v>78.13699758388174</v>
       </c>
       <c r="C12" t="n">
-        <v>35.29532668612821</v>
+        <v>35.9437851217445</v>
       </c>
       <c r="D12" t="n">
-        <v>1.524813607400674</v>
+        <v>1.553583129249602</v>
       </c>
       <c r="E12" t="n">
-        <v>9.481411262202743</v>
+        <v>9.674858043587376</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538327522016742</v>
+        <v>0.7539284243711151</v>
       </c>
       <c r="G12" t="n">
-        <v>23.5761674463671</v>
+        <v>24.00370820674602</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67630660127701</v>
+        <v>34.68070752107129</v>
       </c>
       <c r="I12" t="n">
-        <v>2.691138149916156</v>
+        <v>2.758159606536864</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711454701260466</v>
+        <v>4.71205265231947</v>
       </c>
       <c r="K12" t="n">
-        <v>22.58487547937419</v>
+        <v>21.86300241611826</v>
       </c>
       <c r="L12" t="n">
-        <v>42.03019705420716</v>
+        <v>42.10138185960169</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91039921970956</v>
+        <v>99.90816939746445</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74.80424292515733</v>
+        <v>75.51451855211353</v>
       </c>
       <c r="C13" t="n">
-        <v>33.09911266019206</v>
+        <v>33.74667649531604</v>
       </c>
       <c r="D13" t="n">
-        <v>1.411104258735382</v>
+        <v>1.439403706509241</v>
       </c>
       <c r="E13" t="n">
-        <v>9.148500643198419</v>
+        <v>9.347278414682425</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545868305681461</v>
+        <v>0.7546941221773823</v>
       </c>
       <c r="G13" t="n">
-        <v>21.81803082472439</v>
+        <v>22.23957373909244</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71099420613471</v>
+        <v>34.71592962015958</v>
       </c>
       <c r="I13" t="n">
-        <v>2.244858470745357</v>
+        <v>2.30080068588383</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716167691050915</v>
+        <v>4.71683826360864</v>
       </c>
       <c r="K13" t="n">
-        <v>25.19575707484268</v>
+        <v>24.48548144788646</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6303764274676</v>
+        <v>41.69122651217148</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92524616250233</v>
+        <v>99.92338445537398</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.29743955628688</v>
+        <v>82.6385183436963</v>
       </c>
       <c r="C14" t="n">
-        <v>37.84894468787268</v>
+        <v>38.08503074819455</v>
       </c>
       <c r="D14" t="n">
-        <v>1.412708197805398</v>
+        <v>1.441220335697817</v>
       </c>
       <c r="E14" t="n">
-        <v>11.75380058605453</v>
+        <v>11.77457087429034</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554445356539152</v>
+        <v>0.7556465994876701</v>
       </c>
       <c r="G14" t="n">
-        <v>23.97001257020693</v>
+        <v>24.16165893868254</v>
       </c>
       <c r="H14" t="n">
-        <v>36.87763080618786</v>
+        <v>36.65376086247425</v>
       </c>
       <c r="I14" t="n">
-        <v>2.806314512541284</v>
+        <v>3.128869486265759</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721528347836971</v>
+        <v>4.722791246797938</v>
       </c>
       <c r="K14" t="n">
-        <v>17.70256044371312</v>
+        <v>17.3614816563037</v>
       </c>
       <c r="L14" t="n">
-        <v>44.35505725768068</v>
+        <v>44.44932340852397</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90656238926648</v>
+        <v>99.8958358130222</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.39183620398144</v>
+        <v>81.76502795879678</v>
       </c>
       <c r="C15" t="n">
-        <v>37.37612844193497</v>
+        <v>37.69417156968465</v>
       </c>
       <c r="D15" t="n">
-        <v>1.379579489392634</v>
+        <v>1.409037563796497</v>
       </c>
       <c r="E15" t="n">
-        <v>11.86830768991053</v>
+        <v>11.94666970141617</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561687576730997</v>
+        <v>0.7564506771058249</v>
       </c>
       <c r="G15" t="n">
-        <v>23.40790387831834</v>
+        <v>23.6221236996071</v>
       </c>
       <c r="H15" t="n">
-        <v>36.91298428481495</v>
+        <v>36.6927638418441</v>
       </c>
       <c r="I15" t="n">
-        <v>2.340837368415011</v>
+        <v>2.610165743115683</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726054735456874</v>
+        <v>4.727816731911406</v>
       </c>
       <c r="K15" t="n">
-        <v>18.60816379601855</v>
+        <v>18.23497204120322</v>
       </c>
       <c r="L15" t="n">
-        <v>43.93775458114257</v>
+        <v>43.98394334782699</v>
       </c>
       <c r="M15" t="n">
-        <v>99.9220468190961</v>
+        <v>99.91308695871486</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.79777406252714</v>
+        <v>79.17277223311829</v>
       </c>
       <c r="C16" t="n">
-        <v>35.14301397500905</v>
+        <v>35.50454893612428</v>
       </c>
       <c r="D16" t="n">
-        <v>1.283007942755337</v>
+        <v>1.311460853292392</v>
       </c>
       <c r="E16" t="n">
-        <v>11.36290250632931</v>
+        <v>11.4822108541118</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567932571019875</v>
+        <v>0.7571440522158518</v>
       </c>
       <c r="G16" t="n">
-        <v>21.76933393838571</v>
+        <v>21.98627722897204</v>
       </c>
       <c r="H16" t="n">
-        <v>36.94346972522822</v>
+        <v>36.72639703160258</v>
       </c>
       <c r="I16" t="n">
-        <v>1.952308835839144</v>
+        <v>2.177131886574558</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729957856887423</v>
+        <v>4.732150326349074</v>
       </c>
       <c r="K16" t="n">
-        <v>21.20222593747286</v>
+        <v>20.82722776688171</v>
       </c>
       <c r="L16" t="n">
-        <v>43.58973682728434</v>
+        <v>43.59571869301858</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93497673976626</v>
+        <v>99.92749539602455</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.78152292615937</v>
+        <v>80.87335560641462</v>
       </c>
       <c r="C17" t="n">
-        <v>36.57834015966233</v>
+        <v>36.72777546608573</v>
       </c>
       <c r="D17" t="n">
-        <v>1.284026678483953</v>
+        <v>1.312652086936426</v>
       </c>
       <c r="E17" t="n">
-        <v>12.23599010787438</v>
+        <v>12.27217081976205</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573941671232691</v>
+        <v>0.7578317856438956</v>
       </c>
       <c r="G17" t="n">
-        <v>22.32997319006605</v>
+        <v>22.41848155740373</v>
       </c>
       <c r="H17" t="n">
-        <v>37.51615756504414</v>
+        <v>37.17199019019411</v>
       </c>
       <c r="I17" t="n">
-        <v>1.924267673047147</v>
+        <v>2.203780506200054</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733713544520433</v>
+        <v>4.736448660274348</v>
       </c>
       <c r="K17" t="n">
-        <v>19.21847707384063</v>
+        <v>19.12664439358538</v>
       </c>
       <c r="L17" t="n">
-        <v>44.13909140064312</v>
+        <v>44.07218745458748</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93590863414609</v>
+        <v>99.92660731425859</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.22277424962685</v>
+        <v>78.45424090585709</v>
       </c>
       <c r="C18" t="n">
-        <v>34.31589486604943</v>
+        <v>34.6481021750497</v>
       </c>
       <c r="D18" t="n">
-        <v>1.193196208478388</v>
+        <v>1.225409232751165</v>
       </c>
       <c r="E18" t="n">
-        <v>11.63787334766178</v>
+        <v>11.76284462371639</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579120703205871</v>
+        <v>0.7584235669353977</v>
       </c>
       <c r="G18" t="n">
-        <v>20.75037831555759</v>
+        <v>20.92848101801307</v>
       </c>
       <c r="H18" t="n">
-        <v>37.54181096824873</v>
+        <v>37.20101732890638</v>
       </c>
       <c r="I18" t="n">
-        <v>1.604652899856102</v>
+        <v>1.837917842188453</v>
       </c>
       <c r="J18" t="n">
-        <v>4.73695043950367</v>
+        <v>4.740147293346237</v>
       </c>
       <c r="K18" t="n">
-        <v>21.77722575037317</v>
+        <v>21.54575909414291</v>
       </c>
       <c r="L18" t="n">
-        <v>43.85342750377053</v>
+        <v>43.74492260563517</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94654812019313</v>
+        <v>99.93878387482778</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.23761006336923</v>
+        <v>77.50627514011343</v>
       </c>
       <c r="C19" t="n">
-        <v>33.56741827017218</v>
+        <v>33.98245904264297</v>
       </c>
       <c r="D19" t="n">
-        <v>1.158467138119034</v>
+        <v>1.191944428768776</v>
       </c>
       <c r="E19" t="n">
-        <v>11.52369711709511</v>
+        <v>11.69704673021793</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583527694973885</v>
+        <v>0.7589234687467685</v>
       </c>
       <c r="G19" t="n">
-        <v>20.14641951700995</v>
+        <v>20.35694336659146</v>
       </c>
       <c r="H19" t="n">
-        <v>37.56364020918211</v>
+        <v>37.22553773776274</v>
       </c>
       <c r="I19" t="n">
-        <v>1.347328503106956</v>
+        <v>1.532607728358439</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739704809358679</v>
+        <v>4.743271679667304</v>
       </c>
       <c r="K19" t="n">
-        <v>22.76238993663076</v>
+        <v>22.49372485988658</v>
       </c>
       <c r="L19" t="n">
-        <v>43.6253069420537</v>
+        <v>43.47276282407633</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95511514885663</v>
+        <v>99.94894672660587</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.61200436817748</v>
+        <v>75.05195496688161</v>
       </c>
       <c r="C20" t="n">
-        <v>31.14845980529459</v>
+        <v>31.76340000558734</v>
       </c>
       <c r="D20" t="n">
-        <v>1.066348685045668</v>
+        <v>1.10457787652187</v>
       </c>
       <c r="E20" t="n">
-        <v>10.79458398042581</v>
+        <v>11.05266539061263</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587333543209074</v>
+        <v>0.7593542044813464</v>
       </c>
       <c r="G20" t="n">
-        <v>18.54442586539259</v>
+        <v>18.86483021660028</v>
       </c>
       <c r="H20" t="n">
-        <v>37.5824917937675</v>
+        <v>37.24666551942037</v>
       </c>
       <c r="I20" t="n">
-        <v>1.123337224719342</v>
+        <v>1.277897981236707</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742083464505672</v>
+        <v>4.745963778008416</v>
       </c>
       <c r="K20" t="n">
-        <v>25.38799563182252</v>
+        <v>24.94804503311839</v>
       </c>
       <c r="L20" t="n">
-        <v>43.42611877112992</v>
+        <v>43.24598252439541</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96257420824702</v>
+        <v>99.95742756310115</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.05387937427153</v>
+        <v>81.03947713545023</v>
       </c>
       <c r="C21" t="n">
-        <v>35.24286851960184</v>
+        <v>35.44620190122957</v>
       </c>
       <c r="D21" t="n">
-        <v>1.067017083486278</v>
+        <v>1.105424194001552</v>
       </c>
       <c r="E21" t="n">
-        <v>12.96903030027275</v>
+        <v>13.05015417454855</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592089362745206</v>
+        <v>0.7599360147368136</v>
       </c>
       <c r="G21" t="n">
-        <v>20.46970279591026</v>
+        <v>20.55784607407073</v>
       </c>
       <c r="H21" t="n">
-        <v>39.51970198191206</v>
+        <v>38.95376537119859</v>
       </c>
       <c r="I21" t="n">
-        <v>1.524162424699905</v>
+        <v>1.862751214788921</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745055851715755</v>
+        <v>4.749600092105085</v>
       </c>
       <c r="K21" t="n">
-        <v>18.94612062572848</v>
+        <v>18.96052286454978</v>
       </c>
       <c r="L21" t="n">
-        <v>45.76023726592624</v>
+        <v>45.53123106473696</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94922641125656</v>
+        <v>99.9379558305163</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_41_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_41_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.35696290104448</v>
+        <v>43.52861558114731</v>
       </c>
       <c r="M2" t="n">
-        <v>99.54986714336655</v>
+        <v>97.38304925808248</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.95498805520982</v>
+        <v>81.44264715137876</v>
       </c>
       <c r="C3" t="n">
-        <v>45.87319237513621</v>
+        <v>43.19820270693432</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228587073419041</v>
+        <v>2.178033861243083</v>
       </c>
       <c r="E3" t="n">
-        <v>5.67078464309845</v>
+        <v>4.15231573742709</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742862357806347</v>
+        <v>0.7376087934370488</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95460073554845</v>
+        <v>32.76125932953138</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17166845909196</v>
+        <v>33.93000449810424</v>
       </c>
       <c r="I3" t="n">
-        <v>6.543595049955898</v>
+        <v>3.07336997265437</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642889736289669</v>
+        <v>4.610054958981554</v>
       </c>
       <c r="K3" t="n">
-        <v>12.0450119447902</v>
+        <v>18.55735284862124</v>
       </c>
       <c r="L3" t="n">
-        <v>48.8468990452325</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7651033651589</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.95732373419496</v>
+        <v>88.54763822783944</v>
       </c>
       <c r="C4" t="n">
-        <v>42.50800313468465</v>
+        <v>42.78267609083218</v>
       </c>
       <c r="D4" t="n">
-        <v>2.180021603018752</v>
+        <v>2.183781673081808</v>
       </c>
       <c r="E4" t="n">
-        <v>6.457943001628195</v>
+        <v>6.526902713774886</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444184124924271</v>
+        <v>0.7395553364319523</v>
       </c>
       <c r="G4" t="n">
-        <v>33.21466053906961</v>
+        <v>33.44533946629834</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24324697465165</v>
+        <v>34.0195454758698</v>
       </c>
       <c r="I4" t="n">
-        <v>5.464418125256652</v>
+        <v>7.010292709682967</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65261507807767</v>
+        <v>4.622220852699702</v>
       </c>
       <c r="K4" t="n">
-        <v>13.04267626580504</v>
+        <v>11.45236177216054</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26755407034488</v>
+        <v>45.53190076023563</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81823347083457</v>
+        <v>99.76693862322836</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.7456224826677</v>
+        <v>87.49829815043907</v>
       </c>
       <c r="C5" t="n">
-        <v>42.14428926652293</v>
+        <v>42.81989087742035</v>
       </c>
       <c r="D5" t="n">
-        <v>2.120660503299093</v>
+        <v>2.134173049538549</v>
       </c>
       <c r="E5" t="n">
-        <v>7.042388700157625</v>
+        <v>7.354455587793156</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457385405252581</v>
+        <v>0.7412049124503713</v>
       </c>
       <c r="G5" t="n">
-        <v>32.3102388701815</v>
+        <v>32.68556696920681</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30397286416187</v>
+        <v>34.09542597271707</v>
       </c>
       <c r="I5" t="n">
-        <v>4.561757126059486</v>
+        <v>5.854940955918289</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660865878282864</v>
+        <v>4.632530702814821</v>
       </c>
       <c r="K5" t="n">
-        <v>14.2543775173323</v>
+        <v>12.50170184956092</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44954382377652</v>
+        <v>44.48367691997197</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84821060763176</v>
+        <v>99.80526964695323</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.30246090862134</v>
+        <v>86.13735601352103</v>
       </c>
       <c r="C6" t="n">
-        <v>41.40944241873646</v>
+        <v>42.36764462594837</v>
       </c>
       <c r="D6" t="n">
-        <v>2.049948371937061</v>
+        <v>2.069211163552701</v>
       </c>
       <c r="E6" t="n">
-        <v>7.442095688952925</v>
+        <v>7.945318566742101</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468611514797835</v>
+        <v>0.7426070400696508</v>
       </c>
       <c r="G6" t="n">
-        <v>31.23287365695073</v>
+        <v>31.6906541736884</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35561296807003</v>
+        <v>34.15992384320393</v>
       </c>
       <c r="I6" t="n">
-        <v>3.807186874482162</v>
+        <v>4.888347225828925</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667882196748647</v>
+        <v>4.641294000435317</v>
       </c>
       <c r="K6" t="n">
-        <v>15.69753909137868</v>
+        <v>13.86264398647898</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76630301416097</v>
+        <v>43.60707413879713</v>
       </c>
       <c r="M6" t="n">
-        <v>99.8732845242761</v>
+        <v>99.83736275122448</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.67196048747341</v>
+        <v>84.62478797892828</v>
       </c>
       <c r="C7" t="n">
-        <v>40.3700544029618</v>
+        <v>41.61416002415859</v>
       </c>
       <c r="D7" t="n">
-        <v>1.970395304221247</v>
+        <v>1.997369737334275</v>
       </c>
       <c r="E7" t="n">
-        <v>7.682740902333238</v>
+        <v>8.349491469539009</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478177709999619</v>
+        <v>0.743800529110406</v>
       </c>
       <c r="G7" t="n">
-        <v>30.02080854008974</v>
+        <v>30.59037894139952</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39961746599824</v>
+        <v>34.21482433907866</v>
       </c>
       <c r="I7" t="n">
-        <v>3.176719435081222</v>
+        <v>4.080169655526376</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673861068749763</v>
+        <v>4.648753306940036</v>
       </c>
       <c r="K7" t="n">
-        <v>17.32803951252657</v>
+        <v>15.37521202107171</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19615089355382</v>
+        <v>42.87484053183001</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89424480904219</v>
+        <v>99.86421257706031</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.57142461651272</v>
+        <v>82.91627886468144</v>
       </c>
       <c r="C8" t="n">
-        <v>42.63588308356096</v>
+        <v>40.53922179307058</v>
       </c>
       <c r="D8" t="n">
-        <v>1.974659317529403</v>
+        <v>1.916629669642337</v>
       </c>
       <c r="E8" t="n">
-        <v>9.494488036955628</v>
+        <v>8.579444239822262</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494360782100877</v>
+        <v>0.7448186197451088</v>
       </c>
       <c r="G8" t="n">
-        <v>30.50956538682441</v>
+        <v>29.3538180682249</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47405959766403</v>
+        <v>34.26165650827499</v>
       </c>
       <c r="I8" t="n">
-        <v>5.685240710516106</v>
+        <v>3.404795385564924</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683975488813049</v>
+        <v>4.655116373406929</v>
       </c>
       <c r="K8" t="n">
-        <v>12.42857538348728</v>
+        <v>17.08372113531855</v>
       </c>
       <c r="L8" t="n">
-        <v>44.74644272655807</v>
+        <v>42.26371902562401</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81090119360631</v>
+        <v>99.88666195401315</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.51552608909526</v>
+        <v>80.98043375616088</v>
       </c>
       <c r="C9" t="n">
-        <v>41.46186705745152</v>
+        <v>39.13175373690915</v>
       </c>
       <c r="D9" t="n">
-        <v>1.88142526579664</v>
+        <v>1.825655009254578</v>
       </c>
       <c r="E9" t="n">
-        <v>9.83728098765541</v>
+        <v>8.645653896825888</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508226384529815</v>
+        <v>0.7456895160652304</v>
       </c>
       <c r="G9" t="n">
-        <v>29.06904834554651</v>
+        <v>27.96051101880457</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53784136883714</v>
+        <v>34.30171773900058</v>
       </c>
       <c r="I9" t="n">
-        <v>4.74646599247543</v>
+        <v>2.840647100802324</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692641490331135</v>
+        <v>4.660559475407688</v>
       </c>
       <c r="K9" t="n">
-        <v>14.48447391090476</v>
+        <v>19.01956624383914</v>
       </c>
       <c r="L9" t="n">
-        <v>43.89573567857384</v>
+        <v>41.75410236965268</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84207664693011</v>
+        <v>99.90542235040097</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.15332705536431</v>
+        <v>85.73984952393495</v>
       </c>
       <c r="C10" t="n">
-        <v>39.83560959156441</v>
+        <v>42.41987778781225</v>
       </c>
       <c r="D10" t="n">
-        <v>1.775278464717587</v>
+        <v>1.827701806665497</v>
       </c>
       <c r="E10" t="n">
-        <v>9.942556703010819</v>
+        <v>10.51866242386985</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520150186546708</v>
+        <v>0.7465255312833819</v>
       </c>
       <c r="G10" t="n">
-        <v>27.42902227149165</v>
+        <v>29.3745462424076</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59269085811486</v>
+        <v>35.72286228250862</v>
       </c>
       <c r="I10" t="n">
-        <v>3.96166987278303</v>
+        <v>2.883766666678854</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700093866591693</v>
+        <v>4.665784570521136</v>
       </c>
       <c r="K10" t="n">
-        <v>16.8466729446357</v>
+        <v>14.26015047606507</v>
       </c>
       <c r="L10" t="n">
-        <v>43.18587118623113</v>
+        <v>43.22395382916537</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86815372243125</v>
+        <v>99.90398209304269</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.66341344914107</v>
+        <v>85.30980475956666</v>
       </c>
       <c r="C11" t="n">
-        <v>37.95919077842694</v>
+        <v>42.32825862359743</v>
       </c>
       <c r="D11" t="n">
-        <v>1.664633891597228</v>
+        <v>1.800941008492001</v>
       </c>
       <c r="E11" t="n">
-        <v>9.873868551798044</v>
+        <v>10.82572497633146</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530423690628808</v>
+        <v>0.7472438743003674</v>
       </c>
       <c r="G11" t="n">
-        <v>25.71950316186802</v>
+        <v>28.99507906468337</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63994897689252</v>
+        <v>35.80786486239354</v>
       </c>
       <c r="I11" t="n">
-        <v>3.305901691279391</v>
+        <v>2.462676758988633</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706514806643006</v>
+        <v>4.670274214377296</v>
       </c>
       <c r="K11" t="n">
-        <v>19.3365865508589</v>
+        <v>14.69019524043334</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59417628535908</v>
+        <v>42.89953582496224</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88995361464492</v>
+        <v>99.91798968899302</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.13699758388174</v>
+        <v>83.23800294434054</v>
       </c>
       <c r="C12" t="n">
-        <v>35.9437851217445</v>
+        <v>40.63922554732949</v>
       </c>
       <c r="D12" t="n">
-        <v>1.553583129249602</v>
+        <v>1.71270328687374</v>
       </c>
       <c r="E12" t="n">
-        <v>9.674858043587376</v>
+        <v>10.63763464102014</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539284243711151</v>
+        <v>0.7478584886371128</v>
       </c>
       <c r="G12" t="n">
-        <v>24.00370820674602</v>
+        <v>27.57445523372775</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68070752107129</v>
+        <v>35.83731713074873</v>
       </c>
       <c r="I12" t="n">
-        <v>2.758159606536864</v>
+        <v>2.053918609351117</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71205265231947</v>
+        <v>4.674115553981954</v>
       </c>
       <c r="K12" t="n">
-        <v>21.86300241611826</v>
+        <v>16.76199705565947</v>
       </c>
       <c r="L12" t="n">
-        <v>42.10138185960169</v>
+        <v>42.53036970926136</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90816939746445</v>
+        <v>99.9315923122503</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.51451855211353</v>
+        <v>84.3388660975436</v>
       </c>
       <c r="C13" t="n">
-        <v>33.74667649531604</v>
+        <v>41.5764827183483</v>
       </c>
       <c r="D13" t="n">
-        <v>1.439403706509241</v>
+        <v>1.713986132321045</v>
       </c>
       <c r="E13" t="n">
-        <v>9.347278414682425</v>
+        <v>11.25578475121543</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546941221773823</v>
+        <v>0.748418648044016</v>
       </c>
       <c r="G13" t="n">
-        <v>22.23957373909244</v>
+        <v>27.88943471722376</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71592962015958</v>
+        <v>36.15848564584614</v>
       </c>
       <c r="I13" t="n">
-        <v>2.30080068588383</v>
+        <v>1.895139652618105</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71683826360864</v>
+        <v>4.6776165502751</v>
       </c>
       <c r="K13" t="n">
-        <v>24.48548144788646</v>
+        <v>15.6611339024564</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69122651217148</v>
+        <v>42.69925933847883</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92338445537398</v>
+        <v>99.93687595928353</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.6385183436963</v>
+        <v>82.27422122308144</v>
       </c>
       <c r="C14" t="n">
-        <v>38.08503074819455</v>
+        <v>39.80619321498349</v>
       </c>
       <c r="D14" t="n">
-        <v>1.441220335697817</v>
+        <v>1.628419123718899</v>
       </c>
       <c r="E14" t="n">
-        <v>11.77457087429034</v>
+        <v>10.95724668222269</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556465994876701</v>
+        <v>0.7488978267473714</v>
       </c>
       <c r="G14" t="n">
-        <v>24.16165893868254</v>
+        <v>26.49711569237492</v>
       </c>
       <c r="H14" t="n">
-        <v>36.65376086247425</v>
+        <v>36.18163629329774</v>
       </c>
       <c r="I14" t="n">
-        <v>3.128869486265759</v>
+        <v>1.580294187548755</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722791246797938</v>
+        <v>4.680611417171071</v>
       </c>
       <c r="K14" t="n">
-        <v>17.3614816563037</v>
+        <v>17.72577877691856</v>
       </c>
       <c r="L14" t="n">
-        <v>44.44932340852397</v>
+        <v>42.41538523996966</v>
       </c>
       <c r="M14" t="n">
-        <v>99.8958358130222</v>
+        <v>99.94735723187171</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.76502795879678</v>
+        <v>81.32371273078378</v>
       </c>
       <c r="C15" t="n">
-        <v>37.69417156968465</v>
+        <v>39.07513369606666</v>
       </c>
       <c r="D15" t="n">
-        <v>1.409037563796497</v>
+        <v>1.588453901112758</v>
       </c>
       <c r="E15" t="n">
-        <v>11.94666970141617</v>
+        <v>10.9120550169078</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564506771058249</v>
+        <v>0.7493098764469134</v>
       </c>
       <c r="G15" t="n">
-        <v>23.6221236996071</v>
+        <v>25.84681435923408</v>
       </c>
       <c r="H15" t="n">
-        <v>36.6927638418441</v>
+        <v>36.20154372503425</v>
       </c>
       <c r="I15" t="n">
-        <v>2.610165743115683</v>
+        <v>1.342349124254762</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727816731911406</v>
+        <v>4.683186727793208</v>
       </c>
       <c r="K15" t="n">
-        <v>18.23497204120322</v>
+        <v>18.67628726921624</v>
       </c>
       <c r="L15" t="n">
-        <v>43.98394334782699</v>
+        <v>42.20385866941879</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91308695871486</v>
+        <v>99.95527963470167</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.17277223311829</v>
+        <v>78.87179783942736</v>
       </c>
       <c r="C16" t="n">
-        <v>35.50454893612428</v>
+        <v>36.83115564071387</v>
       </c>
       <c r="D16" t="n">
-        <v>1.311460853292392</v>
+        <v>1.487591970293144</v>
       </c>
       <c r="E16" t="n">
-        <v>11.4822108541118</v>
+        <v>10.40569868907274</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7571440522158518</v>
+        <v>0.7496642881590073</v>
       </c>
       <c r="G16" t="n">
-        <v>21.98627722897204</v>
+        <v>24.20562124687354</v>
       </c>
       <c r="H16" t="n">
-        <v>36.72639703160258</v>
+        <v>36.21866648224768</v>
       </c>
       <c r="I16" t="n">
-        <v>2.177131886574558</v>
+        <v>1.11915336178744</v>
       </c>
       <c r="J16" t="n">
-        <v>4.732150326349074</v>
+        <v>4.685401800993795</v>
       </c>
       <c r="K16" t="n">
-        <v>20.82722776688171</v>
+        <v>21.12820216057265</v>
       </c>
       <c r="L16" t="n">
-        <v>43.59571869301858</v>
+        <v>42.00335472303976</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92749539602455</v>
+        <v>99.96271252432626</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.87335560641462</v>
+        <v>83.82188757396429</v>
       </c>
       <c r="C17" t="n">
-        <v>36.72777546608573</v>
+        <v>40.10475411126787</v>
       </c>
       <c r="D17" t="n">
-        <v>1.312652086936426</v>
+        <v>1.48833022570738</v>
       </c>
       <c r="E17" t="n">
-        <v>12.27217081976205</v>
+        <v>12.14375658924937</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7578317856438956</v>
+        <v>0.7500363281610003</v>
       </c>
       <c r="G17" t="n">
-        <v>22.41848155740373</v>
+        <v>25.7425339741158</v>
       </c>
       <c r="H17" t="n">
-        <v>37.17199019019411</v>
+        <v>37.76154098924111</v>
       </c>
       <c r="I17" t="n">
-        <v>2.203780506200054</v>
+        <v>1.247962416483374</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736448660274348</v>
+        <v>4.687727051006251</v>
       </c>
       <c r="K17" t="n">
-        <v>19.12664439358538</v>
+        <v>16.17811242603572</v>
       </c>
       <c r="L17" t="n">
-        <v>44.07218745458748</v>
+        <v>43.67555534967816</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92660731425859</v>
+        <v>99.95842188698175</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.45424090585709</v>
+        <v>85.44350897940805</v>
       </c>
       <c r="C18" t="n">
-        <v>34.6481021750497</v>
+        <v>40.8521531753733</v>
       </c>
       <c r="D18" t="n">
-        <v>1.225409232751165</v>
+        <v>1.489534837626593</v>
       </c>
       <c r="E18" t="n">
-        <v>11.76284462371639</v>
+        <v>12.75423453450263</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7584235669353977</v>
+        <v>0.7506433861143628</v>
       </c>
       <c r="G18" t="n">
-        <v>20.92848101801307</v>
+        <v>25.89080498155942</v>
       </c>
       <c r="H18" t="n">
-        <v>37.20101732890638</v>
+        <v>37.79210410055726</v>
       </c>
       <c r="I18" t="n">
-        <v>1.837917842188453</v>
+        <v>2.074665975833016</v>
       </c>
       <c r="J18" t="n">
-        <v>4.740147293346237</v>
+        <v>4.691521163214766</v>
       </c>
       <c r="K18" t="n">
-        <v>21.54575909414291</v>
+        <v>14.55649102059197</v>
       </c>
       <c r="L18" t="n">
-        <v>43.74492260563517</v>
+        <v>44.52225619875126</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93878387482778</v>
+        <v>99.93090039471653</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.50627514011343</v>
+        <v>82.72466670474395</v>
       </c>
       <c r="C19" t="n">
-        <v>33.98245904264297</v>
+        <v>38.45452351733796</v>
       </c>
       <c r="D19" t="n">
-        <v>1.191944428768776</v>
+        <v>1.389597117658543</v>
       </c>
       <c r="E19" t="n">
-        <v>11.69704673021793</v>
+        <v>12.1868605306394</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7589234687467685</v>
+        <v>0.7511666815830468</v>
       </c>
       <c r="G19" t="n">
-        <v>20.35694336659146</v>
+        <v>24.15370696100066</v>
       </c>
       <c r="H19" t="n">
-        <v>37.22553773776274</v>
+        <v>37.81845008214277</v>
       </c>
       <c r="I19" t="n">
-        <v>1.532607728358439</v>
+        <v>1.730093571825497</v>
       </c>
       <c r="J19" t="n">
-        <v>4.743271679667304</v>
+        <v>4.694791759894041</v>
       </c>
       <c r="K19" t="n">
-        <v>22.49372485988658</v>
+        <v>17.27533329525604</v>
       </c>
       <c r="L19" t="n">
-        <v>43.47276282407633</v>
+        <v>44.21251357696621</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94894672660587</v>
+        <v>99.94237038956021</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.05195496688161</v>
+        <v>79.82782375382291</v>
       </c>
       <c r="C20" t="n">
-        <v>31.76340000558734</v>
+        <v>35.82477911382524</v>
       </c>
       <c r="D20" t="n">
-        <v>1.10457787652187</v>
+        <v>1.283679567880848</v>
       </c>
       <c r="E20" t="n">
-        <v>11.05266539061263</v>
+        <v>11.49839199030309</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7593542044813464</v>
+        <v>0.7516191733191746</v>
       </c>
       <c r="G20" t="n">
-        <v>18.86483021660028</v>
+        <v>22.31266870117153</v>
       </c>
       <c r="H20" t="n">
-        <v>37.24666551942037</v>
+        <v>37.84123135899503</v>
       </c>
       <c r="I20" t="n">
-        <v>1.277897981236707</v>
+        <v>1.442613128908386</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745963778008416</v>
+        <v>4.69761983324484</v>
       </c>
       <c r="K20" t="n">
-        <v>24.94804503311839</v>
+        <v>20.17217624617711</v>
       </c>
       <c r="L20" t="n">
-        <v>43.24598252439541</v>
+        <v>43.95498648522473</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95742756310115</v>
+        <v>99.95194184522707</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.03947713545023</v>
+        <v>76.82335180208526</v>
       </c>
       <c r="C21" t="n">
-        <v>35.44620190122957</v>
+        <v>33.04225041550761</v>
       </c>
       <c r="D21" t="n">
-        <v>1.105424194001552</v>
+        <v>1.174395937269345</v>
       </c>
       <c r="E21" t="n">
-        <v>13.05015417454855</v>
+        <v>10.71996565164549</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7599360147368136</v>
+        <v>0.7520114374287179</v>
       </c>
       <c r="G21" t="n">
-        <v>20.55784607407073</v>
+        <v>20.41312187865639</v>
       </c>
       <c r="H21" t="n">
-        <v>38.95376537119859</v>
+        <v>37.8609803987348</v>
       </c>
       <c r="I21" t="n">
-        <v>1.862751214788921</v>
+        <v>1.202805014421013</v>
       </c>
       <c r="J21" t="n">
-        <v>4.749600092105085</v>
+        <v>4.700071483929485</v>
       </c>
       <c r="K21" t="n">
-        <v>18.96052286454978</v>
+        <v>23.17664819791474</v>
       </c>
       <c r="L21" t="n">
-        <v>45.53123106473696</v>
+        <v>43.74102879966352</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9379558305163</v>
+        <v>99.95992741308588</v>
       </c>
     </row>
   </sheetData>
